--- a/output/pdf_financials_xlsx/CRD.xlsx
+++ b/output/pdf_financials_xlsx/CRD.xlsx
@@ -6031,46 +6031,46 @@
         <v>2.94678</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.144111</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.218841</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.218841</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.148635</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.105525</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.063525</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.056925</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.105559</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.090748</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.82994</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.8434970000000001</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.806774</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.689597</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.896553</v>
       </c>
     </row>
     <row r="93">
@@ -9570,7 +9570,11 @@
           <t>Reserves (notes 9 and 10)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -10372,7 +10376,11 @@
           <t>Reserves (notes 10 and 11)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11077,7 +11085,11 @@
           <t>Reserves (notes 10 and 11)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11689,7 +11701,11 @@
           <t>Reserves (notes 10 and 11)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -12087,7 +12103,11 @@
           <t>Reserves (notes 11 and 12)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -12744,7 +12764,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -15962,7 +15986,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -20222,7 +20250,11 @@
           <t>Reserves 3,144,111</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CRD.xlsx
+++ b/output/pdf_financials_xlsx/CRD.xlsx
@@ -1065,28 +1065,28 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002634</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005592</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004862</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00184</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000367</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001401</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000754</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -2069,28 +2069,28 @@
         <v>-3.335435</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.067369</v>
+        <v>-3.070003</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.600492</v>
+        <v>-2.606084</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.324682</v>
+        <v>-3.329544</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.293093</v>
+        <v>-1.294933</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.771129</v>
+        <v>-0.771496</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.516264</v>
+        <v>1.514863</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>0.187424</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.562478</v>
+        <v>-0.563232</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.58005</v>
@@ -2187,28 +2187,28 @@
         <v>-3.335435</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.067369</v>
+        <v>-3.070003</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.600492</v>
+        <v>-2.606084</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.324682</v>
+        <v>-3.329544</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.281886</v>
+        <v>-1.283726</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.760705</v>
+        <v>-0.761072</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.51707</v>
+        <v>1.515669</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0.187424</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.562478</v>
+        <v>-0.563232</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.58005</v>
@@ -2490,55 +2490,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.400642</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.603078</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.603078</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.576561</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.360185</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.185937</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.122785</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.133813</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.220821</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.206627</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.007523</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.031389</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.66091</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.136924</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.011659</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.101098</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.125894</v>
       </c>
     </row>
     <row r="35">
@@ -2606,55 +2606,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.400642</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.603078</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.603078</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.576561</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.360185</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.185937</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.122785</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.525</v>
+        <v>0.658813</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.693264</v>
+        <v>0.914085</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.391475</v>
+        <v>0.598102</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1</v>
+        <v>0.107523</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.025</v>
+        <v>0.056389</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.66091</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.136924</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.011659</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.655143</v>
+        <v>0.7562410000000001</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>3.312309</v>
+        <v>4.438203</v>
       </c>
     </row>
     <row r="37">
@@ -3302,31 +3302,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.036317</v>
+        <v>1.635675</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.764103</v>
+        <v>2.161025</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.764103</v>
+        <v>2.161025</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.860578</v>
+        <v>1.284017</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.148907</v>
+        <v>0.788722</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.687937</v>
+        <v>0.502</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.220094</v>
+        <v>0.09730900000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.214438</v>
+        <v>0.080625</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.297944</v>
+        <v>0.077123</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -19232,7 +19232,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -40112,7 +40112,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">

--- a/output/pdf_financials_xlsx/CRD.xlsx
+++ b/output/pdf_financials_xlsx/CRD.xlsx
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.0595</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>0.0595</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -7332,19 +7332,19 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.29484</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.188609</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.13629</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.01765</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.111375</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -7359,7 +7359,7 @@
         <v>0</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.33255</v>
       </c>
     </row>
     <row r="116">
@@ -23244,7 +23244,11 @@
           <t>Proceeds from sale of marketable securities (note 6)</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -23436,7 +23440,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -26706,7 +26714,11 @@
           <t>Proceeds from sale of marketable securities (note 7)</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -28595,7 +28607,11 @@
           <t>Proceeds from sale of marketable securities (note 8)</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -29813,7 +29829,11 @@
           <t>Acquisition of equipment (note 10)</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -45728,7 +45748,11 @@
           <t>Director fees 44,500</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -48146,7 +48170,11 @@
           <t>Director fees 59,500</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E397" s="5" t="n">
         <v>0.0595</v>
       </c>
